--- a/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Llama-3.1-8B-Instruct/Mistral-7B-Instruct-v0.3/default/total_votes_file.xlsx
+++ b/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Llama-3.1-8B-Instruct/Mistral-7B-Instruct-v0.3/default/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D2">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="E2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="G2">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>310</v>
+        <v>329</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E3">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="G3">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="H3">
         <v>426</v>
